--- a/output/laminas_comunales/comunal_i_ingr_a_2022_nuble.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2022_nuble.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>958912.12</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>895771.3100000001</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>845966.0600000001</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>834095.62</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>822161.5600000001</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>810547.12</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>805094.1899999999</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>792069.75</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>782216.25</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>778773.75</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>776030.8100000001</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>753489.9399999999</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>746916.5600000001</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>746794.0600000001</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -578,9 +531,6 @@
       <c r="B16">
         <v>743819.75</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -591,9 +541,6 @@
       <c r="B17">
         <v>742981.5</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -604,9 +551,6 @@
       <c r="B18">
         <v>716925</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -617,9 +561,6 @@
       <c r="B19">
         <v>711929.38</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -630,9 +571,6 @@
       <c r="B20">
         <v>670110.9399999999</v>
       </c>
-      <c r="F20" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -643,9 +581,6 @@
       <c r="B21">
         <v>668402.0600000001</v>
       </c>
-      <c r="F21" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -655,9 +590,6 @@
       </c>
       <c r="B22">
         <v>667097.6899999999</v>
-      </c>
-      <c r="F22" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_a_2022_nuble.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2022_nuble.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>958912.12</v>
       </c>
+      <c r="C2">
+        <v>870343.5</v>
+      </c>
+      <c r="D2">
+        <v>88568.62</v>
+      </c>
+      <c r="E2">
+        <v>10.17628327206441</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,195 +410,376 @@
       <c r="B3">
         <v>895771.3100000001</v>
       </c>
+      <c r="C3">
+        <v>807321.75</v>
+      </c>
+      <c r="D3">
+        <v>88449.56000000006</v>
+      </c>
+      <c r="E3">
+        <v>10.95592432632964</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ránquil</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B4">
-        <v>845966.0600000001</v>
+        <v>857550.12</v>
+      </c>
+      <c r="C4">
+        <v>768812.88</v>
+      </c>
+      <c r="D4">
+        <v>88737.23999999999</v>
+      </c>
+      <c r="E4">
+        <v>11.54211152133664</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chillán Viejo</t>
+          <t>Ranquil</t>
         </is>
       </c>
       <c r="B5">
-        <v>834095.62</v>
+        <v>845966.0600000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coelemu</t>
+          <t>Chillán Viejo</t>
         </is>
       </c>
       <c r="B6">
-        <v>822161.5600000001</v>
+        <v>834095.62</v>
+      </c>
+      <c r="C6">
+        <v>714509.8100000001</v>
+      </c>
+      <c r="D6">
+        <v>119585.8099999999</v>
+      </c>
+      <c r="E6">
+        <v>16.73676250855114</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Quillón</t>
+          <t>Coelemu</t>
         </is>
       </c>
       <c r="B7">
-        <v>810547.12</v>
+        <v>822161.5600000001</v>
+      </c>
+      <c r="C7">
+        <v>731097.4399999999</v>
+      </c>
+      <c r="D7">
+        <v>91064.12000000011</v>
+      </c>
+      <c r="E7">
+        <v>12.45581163572398</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ñiquén</t>
+          <t>Quillón</t>
         </is>
       </c>
       <c r="B8">
-        <v>805094.1899999999</v>
+        <v>810547.12</v>
+      </c>
+      <c r="C8">
+        <v>718475.12</v>
+      </c>
+      <c r="D8">
+        <v>92072</v>
+      </c>
+      <c r="E8">
+        <v>12.81491835096531</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>San Carlos</t>
+          <t>Ñiquén</t>
         </is>
       </c>
       <c r="B9">
-        <v>792069.75</v>
+        <v>805094.1899999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulnes</t>
+          <t>San Carlos</t>
         </is>
       </c>
       <c r="B10">
-        <v>782216.25</v>
+        <v>792069.75</v>
+      </c>
+      <c r="C10">
+        <v>698125.5</v>
+      </c>
+      <c r="D10">
+        <v>93944.25</v>
+      </c>
+      <c r="E10">
+        <v>13.45664210804505</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pinto</t>
+          <t>Bulnes</t>
         </is>
       </c>
       <c r="B11">
-        <v>778773.75</v>
+        <v>782216.25</v>
+      </c>
+      <c r="C11">
+        <v>694042.4399999999</v>
+      </c>
+      <c r="D11">
+        <v>88173.81000000006</v>
+      </c>
+      <c r="E11">
+        <v>12.7043830345591</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Treguaco</t>
+          <t>Pinto</t>
         </is>
       </c>
       <c r="B12">
-        <v>776030.8100000001</v>
+        <v>778773.75</v>
+      </c>
+      <c r="C12">
+        <v>663808.88</v>
+      </c>
+      <c r="D12">
+        <v>114964.87</v>
+      </c>
+      <c r="E12">
+        <v>17.31897138827068</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cobquecura</t>
+          <t>Treguaco</t>
         </is>
       </c>
       <c r="B13">
-        <v>753489.9399999999</v>
+        <v>776030.8100000001</v>
+      </c>
+      <c r="C13">
+        <v>674094.4399999999</v>
+      </c>
+      <c r="D13">
+        <v>101936.3700000001</v>
+      </c>
+      <c r="E13">
+        <v>15.1219716335296</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
+          <t>Cobquecura</t>
         </is>
       </c>
       <c r="B14">
-        <v>746916.5600000001</v>
+        <v>753489.9399999999</v>
+      </c>
+      <c r="C14">
+        <v>669614.0600000001</v>
+      </c>
+      <c r="D14">
+        <v>83875.87999999989</v>
+      </c>
+      <c r="E14">
+        <v>12.5260034115771</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>San Fabián</t>
+          <t>San Nicolás</t>
         </is>
       </c>
       <c r="B15">
-        <v>746794.0600000001</v>
+        <v>746916.5600000001</v>
+      </c>
+      <c r="C15">
+        <v>648449.8100000001</v>
+      </c>
+      <c r="D15">
+        <v>98466.75</v>
+      </c>
+      <c r="E15">
+        <v>15.18494546247149</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Quirihue</t>
+          <t>San Fabián</t>
         </is>
       </c>
       <c r="B16">
-        <v>743819.75</v>
+        <v>746794.0600000001</v>
+      </c>
+      <c r="C16">
+        <v>651277</v>
+      </c>
+      <c r="D16">
+        <v>95517.06000000006</v>
+      </c>
+      <c r="E16">
+        <v>14.66611902462394</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pemuco</t>
+          <t>Quirihue</t>
         </is>
       </c>
       <c r="B17">
-        <v>742981.5</v>
+        <v>743819.75</v>
+      </c>
+      <c r="C17">
+        <v>659149.9399999999</v>
+      </c>
+      <c r="D17">
+        <v>84669.81000000006</v>
+      </c>
+      <c r="E17">
+        <v>12.8453034525043</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Coihueco</t>
+          <t>Pemuco</t>
         </is>
       </c>
       <c r="B18">
-        <v>716925</v>
+        <v>742981.5</v>
+      </c>
+      <c r="C18">
+        <v>657068.62</v>
+      </c>
+      <c r="D18">
+        <v>85912.88</v>
+      </c>
+      <c r="E18">
+        <v>13.07517622740832</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>El Carmen</t>
+          <t>Coihueco</t>
         </is>
       </c>
       <c r="B19">
-        <v>711929.38</v>
+        <v>716925</v>
+      </c>
+      <c r="C19">
+        <v>624218.6899999999</v>
+      </c>
+      <c r="D19">
+        <v>92706.31000000006</v>
+      </c>
+      <c r="E19">
+        <v>14.85157549512015</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>San Ignacio</t>
+          <t>El Carmen</t>
         </is>
       </c>
       <c r="B20">
-        <v>670110.9399999999</v>
+        <v>711929.38</v>
+      </c>
+      <c r="C20">
+        <v>626336.62</v>
+      </c>
+      <c r="D20">
+        <v>85592.76000000001</v>
+      </c>
+      <c r="E20">
+        <v>13.66561642204476</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ninhue</t>
+          <t>San Ignacio</t>
         </is>
       </c>
       <c r="B21">
-        <v>668402.0600000001</v>
+        <v>670110.9399999999</v>
+      </c>
+      <c r="C21">
+        <v>602792.88</v>
+      </c>
+      <c r="D21">
+        <v>67318.05999999994</v>
+      </c>
+      <c r="E21">
+        <v>11.16769328794991</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>668402.0600000001</v>
+      </c>
+      <c r="C22">
+        <v>627065.0600000001</v>
+      </c>
+      <c r="D22">
+        <v>41337</v>
+      </c>
+      <c r="E22">
+        <v>6.592138940096581</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Portezuelo</t>
         </is>
       </c>
-      <c r="B22">
+      <c r="B23">
         <v>667097.6899999999</v>
+      </c>
+      <c r="C23">
+        <v>579922.75</v>
+      </c>
+      <c r="D23">
+        <v>87174.93999999994</v>
+      </c>
+      <c r="E23">
+        <v>15.0321641977315</v>
       </c>
     </row>
   </sheetData>
@@ -757,7 +947,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ránquil</t>
+          <t>Ranquil</t>
         </is>
       </c>
       <c r="B16">

--- a/output/laminas_comunales/comunal_i_ingr_a_2022_nuble.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2022_nuble.xlsx
@@ -789,7 +789,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -798,11 +798,6 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -810,9 +805,6 @@
           <t>Bulnes</t>
         </is>
       </c>
-      <c r="B2">
-        <v>782216.25</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -820,9 +812,6 @@
           <t>Chillán Viejo</t>
         </is>
       </c>
-      <c r="B3">
-        <v>834095.62</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -830,188 +819,131 @@
           <t>Chillán</t>
         </is>
       </c>
-      <c r="B4">
-        <v>958912.12</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cobquecura</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>753489.9399999999</v>
+          <t>Yungay</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coelemu</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>822161.5600000001</v>
+          <t>Quillón</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Coihueco</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>716925</v>
+          <t>San Carlos</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>El Carmen</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>711929.38</v>
+          <t>Treguaco</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ninhue</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>668402.0600000001</v>
+          <t>Ranquil</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ñiquén</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>805094.1899999999</v>
+          <t>Portezuelo</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pemuco</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>742981.5</v>
+          <t>Cobquecura</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pinto</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>778773.75</v>
+          <t>Quirihue</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Portezuelo</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>667097.6899999999</v>
+          <t>Coelemu</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Quillón</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>810547.12</v>
+          <t>Ninhue</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Quirihue</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>743819.75</v>
+          <t>Pinto</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ranquil</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>845966.0600000001</v>
+          <t>San Ignacio</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>San Carlos</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>792069.75</v>
+          <t>Pemuco</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>San Fabián</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>746794.0600000001</v>
+          <t>San Nicolás</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>San Ignacio</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>670110.9399999999</v>
+          <t>San Fabián</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>746916.5600000001</v>
+          <t>Ñiquén</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Treguaco</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>776030.8100000001</v>
+          <t>El Carmen</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Yungay</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>895771.3100000001</v>
+          <t>Coihueco</t>
+        </is>
       </c>
     </row>
   </sheetData>
